--- a/product_upload/packages/56/file.xlsx
+++ b/product_upload/packages/56/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -825,6 +830,11 @@
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
+        <is>
+          <t>Uroleph</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>SKU-01A887303539</t>
         </is>
@@ -845,7 +855,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1005,6 +1015,11 @@
         </is>
       </c>
       <c r="AT3" t="inlineStr">
+        <is>
+          <t>Uroleph</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>SKU-1177669280B0</t>
         </is>
@@ -1025,7 +1040,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1179,6 +1194,11 @@
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
+        <is>
+          <t>Eptop</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>SKU-298DD2282137</t>
         </is>
@@ -1199,7 +1219,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1353,6 +1373,11 @@
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
+        <is>
+          <t>Eptop</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>SKU-C060B92182FC</t>
         </is>
@@ -1373,7 +1398,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1531,6 +1556,11 @@
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
+        <is>
+          <t>Eptop</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>SKU-40E2521A8B4E</t>
         </is>
@@ -1551,7 +1581,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1709,6 +1739,11 @@
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
+        <is>
+          <t>Uptravi 800 mcg</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>SKU-1F7FFBAE46F2</t>
         </is>
@@ -1729,7 +1764,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1895,6 +1930,11 @@
         </is>
       </c>
       <c r="AT8" t="inlineStr">
+        <is>
+          <t>Uptravi 400 mcg</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>SKU-539697C393F4</t>
         </is>
@@ -1915,7 +1955,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2077,6 +2117,11 @@
         </is>
       </c>
       <c r="AT9" t="inlineStr">
+        <is>
+          <t>Lunginib</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>SKU-57FEDD8A2287</t>
         </is>
@@ -2097,7 +2142,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2261,6 +2306,11 @@
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
+        <is>
+          <t>Adzoy</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
         <is>
           <t>SKU-8BAFF765D063</t>
         </is>
@@ -2281,7 +2331,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2445,6 +2495,11 @@
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
+        <is>
+          <t>Tiotropium Eva</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
         <is>
           <t>SKU-38E8D42C53CB</t>
         </is>
@@ -2465,7 +2520,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2631,6 +2686,11 @@
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
+        <is>
+          <t>Nyvepria</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>SKU-C145A7F62EC4</t>
         </is>
@@ -2651,7 +2711,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2817,6 +2877,11 @@
         </is>
       </c>
       <c r="AT13" t="inlineStr">
+        <is>
+          <t>Orfadin</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>SKU-E0298EF5D6CA</t>
         </is>
@@ -2837,7 +2902,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2997,6 +3062,11 @@
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
+        <is>
+          <t>Sotyktu</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
         <is>
           <t>SKU-4A8DD381A4D4</t>
         </is>
@@ -3017,7 +3087,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3191,6 +3261,11 @@
         </is>
       </c>
       <c r="AT15" t="inlineStr">
+        <is>
+          <t>Mucoplexil</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>SKU-CB15E6C8CC4C</t>
         </is>
@@ -3211,7 +3286,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3373,6 +3448,11 @@
         </is>
       </c>
       <c r="AT16" t="inlineStr">
+        <is>
+          <t>Trientine dihydrochloride Tillomed</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
         <is>
           <t>SKU-25AFB24E3627</t>
         </is>
@@ -3393,7 +3473,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3563,6 +3643,11 @@
         </is>
       </c>
       <c r="AT17" t="inlineStr">
+        <is>
+          <t>Juleen</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>SKU-4F7A05A8A829</t>
         </is>
@@ -3583,7 +3668,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3747,6 +3832,11 @@
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
+        <is>
+          <t>Juleen</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
         <is>
           <t>SKU-018C9741FF39</t>
         </is>
@@ -3767,7 +3857,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3937,6 +4027,11 @@
         </is>
       </c>
       <c r="AT19" t="inlineStr">
+        <is>
+          <t>Juleen</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>SKU-3542B2935C47</t>
         </is>
@@ -3957,7 +4052,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4125,6 +4220,11 @@
         </is>
       </c>
       <c r="AT20" t="inlineStr">
+        <is>
+          <t>Arify</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
         <is>
           <t>SKU-6A9185419321</t>
         </is>
@@ -4145,7 +4245,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4309,6 +4409,11 @@
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
+        <is>
+          <t>Arify</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>SKU-E2DF3B51D3D0</t>
         </is>
@@ -4329,7 +4434,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4491,6 +4596,11 @@
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
+        <is>
+          <t>Jaypirca</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>SKU-7FE1EEB23688</t>
         </is>
@@ -4511,7 +4621,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4665,6 +4775,11 @@
       <c r="AR23" t="inlineStr"/>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
+        <is>
+          <t>Ravopro</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>SKU-158EA1C50EA6</t>
         </is>
@@ -4685,7 +4800,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4841,6 +4956,11 @@
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
+        <is>
+          <t>Warfarin Macleods</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
         <is>
           <t>SKU-1CB66C276B0B</t>
         </is>
@@ -4861,7 +4981,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5025,6 +5145,11 @@
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
+        <is>
+          <t>Propylthiouracil MACLEODS</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
         <is>
           <t>SKU-BAAFDE1475D0</t>
         </is>
@@ -5045,7 +5170,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5211,6 +5336,11 @@
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
+        <is>
+          <t>Tenival</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>SKU-4235BB41AB3F</t>
         </is>
@@ -5231,7 +5361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5397,6 +5527,11 @@
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
+        <is>
+          <t>Tenival</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>SKU-ABBA8E20BFA7</t>
         </is>
@@ -5417,7 +5552,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5575,6 +5710,11 @@
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
+        <is>
+          <t>Trumavar</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>SKU-56D83C0D5DC2</t>
         </is>
@@ -5595,7 +5735,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5753,6 +5893,11 @@
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
+        <is>
+          <t>Trumavar</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>SKU-0248197F7E1D</t>
         </is>
@@ -5773,7 +5918,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5943,6 +6088,11 @@
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
+        <is>
+          <t>VERKAZIA</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
         <is>
           <t>SKU-CB93639546FC</t>
         </is>
@@ -5963,7 +6113,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6129,6 +6279,11 @@
         </is>
       </c>
       <c r="AT31" t="inlineStr">
+        <is>
+          <t>Rivaroxaban MCP</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
         <is>
           <t>SKU-1C7EDA3EEEA5</t>
         </is>
@@ -6149,7 +6304,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6307,6 +6462,11 @@
       <c r="AR32" t="inlineStr"/>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
+        <is>
+          <t>Rivaroxaban MCP</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
         <is>
           <t>SKU-3206F3A6BC80</t>
         </is>
@@ -6327,7 +6487,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6489,6 +6649,11 @@
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
+        <is>
+          <t>Ataben</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
         <is>
           <t>SKU-C32738F481C4</t>
         </is>
@@ -6509,7 +6674,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6671,6 +6836,11 @@
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
+        <is>
+          <t>Ataben</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
         <is>
           <t>SKU-E6D64CD6899C</t>
         </is>
@@ -6691,7 +6861,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6851,6 +7021,11 @@
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
+        <is>
+          <t>Camzyos</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>SKU-C3C79432AA2B</t>
         </is>
@@ -6871,7 +7046,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7035,6 +7210,11 @@
         </is>
       </c>
       <c r="AT36" t="inlineStr">
+        <is>
+          <t>Camzyos</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
         <is>
           <t>SKU-F3419EC34DEE</t>
         </is>
@@ -7055,7 +7235,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7215,6 +7395,11 @@
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
+        <is>
+          <t>Camzyos</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
         <is>
           <t>SKU-CBA8DD903F50</t>
         </is>
@@ -7235,7 +7420,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7395,6 +7580,11 @@
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
+        <is>
+          <t>Camzyos</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
         <is>
           <t>SKU-24F71D8F08F5</t>
         </is>
@@ -7415,7 +7605,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7589,6 +7779,11 @@
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
+        <is>
+          <t>Calquence</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
         <is>
           <t>SKU-F59C37B94A67</t>
         </is>
@@ -7609,7 +7804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7767,6 +7962,11 @@
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
+        <is>
+          <t>Bylvay</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
         <is>
           <t>SKU-B38D78B62117</t>
         </is>
@@ -7787,7 +7987,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7945,6 +8145,11 @@
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
+        <is>
+          <t>Bylvay</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
         <is>
           <t>SKU-6F8357A67261</t>
         </is>
@@ -7965,7 +8170,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8123,6 +8328,11 @@
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
+        <is>
+          <t>Bylvay</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>SKU-1E7A14A375B1</t>
         </is>
@@ -8143,7 +8353,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8301,6 +8511,11 @@
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
+        <is>
+          <t>Bylvay</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>SKU-32E6BB1683C2</t>
         </is>
@@ -8321,7 +8536,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8495,6 +8710,11 @@
         </is>
       </c>
       <c r="AT44" t="inlineStr">
+        <is>
+          <t>Bastix</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
         <is>
           <t>SKU-18640A483542</t>
         </is>
@@ -8515,7 +8735,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8685,6 +8905,11 @@
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
+        <is>
+          <t>Bastix</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
         <is>
           <t>SKU-441F69D23BD3</t>
         </is>
@@ -8705,7 +8930,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8867,6 +9092,11 @@
         </is>
       </c>
       <c r="AT46" t="inlineStr">
+        <is>
+          <t>Zelyssa 18 mg per 3 ml</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
         <is>
           <t>SKU-065A7E8DD4BE</t>
         </is>
@@ -8887,7 +9117,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9045,6 +9275,11 @@
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
+        <is>
+          <t>Evonanz 18 mg per 3 ml</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>SKU-61E0A855F09D</t>
         </is>
@@ -9065,7 +9300,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9227,6 +9462,11 @@
         </is>
       </c>
       <c r="AT48" t="inlineStr">
+        <is>
+          <t>Milorizast 10 mg  - 20 mg - 30 mg starter pack</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
         <is>
           <t>SKU-EBBB195C6575</t>
         </is>
@@ -9247,7 +9487,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9405,6 +9645,11 @@
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
+        <is>
+          <t>Avysk HCT</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>SKU-7DAED710EC6B</t>
         </is>
@@ -9425,7 +9670,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9587,6 +9832,11 @@
         </is>
       </c>
       <c r="AT50" t="inlineStr">
+        <is>
+          <t>Avysk HCT</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>SKU-21721CE3C06B</t>
         </is>
@@ -9607,7 +9857,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9769,6 +10019,11 @@
         </is>
       </c>
       <c r="AT51" t="inlineStr">
+        <is>
+          <t>Avysk HCT</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>SKU-DDA888C20F37</t>
         </is>
@@ -9789,7 +10044,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9957,6 +10212,11 @@
         </is>
       </c>
       <c r="AT52" t="inlineStr">
+        <is>
+          <t>SUNLENCA</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
         <is>
           <t>SKU-F5656248474C</t>
         </is>
@@ -9977,7 +10237,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10143,6 +10403,11 @@
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
+        <is>
+          <t>SUNLENCA</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
         <is>
           <t>SKU-CE30191B7EC3</t>
         </is>
@@ -10163,7 +10428,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10319,6 +10584,11 @@
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
+        <is>
+          <t>Racitam</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
         <is>
           <t>SKU-7FE736D37D3E</t>
         </is>
@@ -10339,7 +10609,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10497,6 +10767,11 @@
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
+        <is>
+          <t>Cymbatex</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
         <is>
           <t>SKU-F325333E0FF7</t>
         </is>
@@ -10517,7 +10792,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10675,6 +10950,11 @@
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
+        <is>
+          <t>Cymbatex</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
         <is>
           <t>SKU-283968271159</t>
         </is>
@@ -10695,7 +10975,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10863,6 +11143,11 @@
         </is>
       </c>
       <c r="AT57" t="inlineStr">
+        <is>
+          <t>Olmy</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
         <is>
           <t>SKU-AAC24487CD50</t>
         </is>
@@ -10883,7 +11168,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11047,6 +11332,11 @@
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
+        <is>
+          <t>Olmy</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
         <is>
           <t>SKU-224FECA41933</t>
         </is>
@@ -11067,7 +11357,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11231,6 +11521,11 @@
         </is>
       </c>
       <c r="AT59" t="inlineStr">
+        <is>
+          <t>PORENZA</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
         <is>
           <t>SKU-9A098BC4A00B</t>
         </is>
@@ -11251,7 +11546,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11419,6 +11714,11 @@
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
+        <is>
+          <t>PORENZA</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
         <is>
           <t>SKU-BC218FE1FC24</t>
         </is>
@@ -11439,7 +11739,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11601,6 +11901,11 @@
         </is>
       </c>
       <c r="AT61" t="inlineStr">
+        <is>
+          <t>Hydroxychloroquine SAJA</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
         <is>
           <t>SKU-BB51C6DAE95E</t>
         </is>
@@ -11621,7 +11926,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11777,6 +12082,11 @@
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
+        <is>
+          <t>Sesmo</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
         <is>
           <t>SKU-D82BFEFE413E</t>
         </is>
@@ -11797,7 +12107,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11953,6 +12263,11 @@
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
+        <is>
+          <t>Sesmo</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
         <is>
           <t>SKU-88D81B49BEB4</t>
         </is>
@@ -11973,7 +12288,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12135,6 +12450,11 @@
         </is>
       </c>
       <c r="AT64" t="inlineStr">
+        <is>
+          <t>Sesmo</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
         <is>
           <t>SKU-27DB62B1BABF</t>
         </is>
@@ -12155,7 +12475,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12311,6 +12631,11 @@
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
+        <is>
+          <t>Sesmo</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
         <is>
           <t>SKU-0565AD17B155</t>
         </is>
@@ -12331,7 +12656,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12491,6 +12816,11 @@
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
+        <is>
+          <t>Simvagen Plus</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
         <is>
           <t>SKU-4D5F60652D30</t>
         </is>
@@ -12511,7 +12841,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12675,6 +13005,11 @@
         </is>
       </c>
       <c r="AT67" t="inlineStr">
+        <is>
+          <t>Simvagen Plus</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>SKU-C5A89340A578</t>
         </is>
@@ -12695,7 +13030,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12857,6 +13192,11 @@
       <c r="AR68" t="inlineStr"/>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
+        <is>
+          <t>Nervamine</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>SKU-2089016874F0</t>
         </is>
@@ -12877,7 +13217,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13047,6 +13387,11 @@
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
+        <is>
+          <t>Jusprin</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>SKU-C90A43D33876</t>
         </is>
@@ -13067,7 +13412,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13237,6 +13582,11 @@
         </is>
       </c>
       <c r="AT70" t="inlineStr">
+        <is>
+          <t>Floxmed</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>SKU-F62258604D16</t>
         </is>
@@ -13257,7 +13607,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13419,6 +13769,11 @@
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
+        <is>
+          <t>Vizarsin</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
         <is>
           <t>SKU-B5E13E4E23A9</t>
         </is>
@@ -13439,7 +13794,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13610,6 +13965,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Sogroya 15 mg / 1.5 ml</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-A515E70A828D</t>
         </is>
       </c>
@@ -13629,7 +13989,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13789,6 +14149,11 @@
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
+        <is>
+          <t>Famotidine for oral suspension</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
         <is>
           <t>SKU-8342D81F4F8B</t>
         </is>
@@ -13809,7 +14174,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13973,6 +14338,11 @@
         </is>
       </c>
       <c r="AT74" t="inlineStr">
+        <is>
+          <t>Famotidine Amarox</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
         <is>
           <t>SKU-C24213F91234</t>
         </is>
@@ -13993,7 +14363,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14157,6 +14527,11 @@
         </is>
       </c>
       <c r="AT75" t="inlineStr">
+        <is>
+          <t>Akeega</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
         <is>
           <t>SKU-FBD5E1DDE95C</t>
         </is>
@@ -14177,7 +14552,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14333,6 +14708,11 @@
       <c r="AR76" t="inlineStr"/>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
+        <is>
+          <t>Akeega</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
         <is>
           <t>SKU-8C0BEA28D021</t>
         </is>
@@ -14353,7 +14733,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14517,6 +14897,11 @@
         </is>
       </c>
       <c r="AT77" t="inlineStr">
+        <is>
+          <t>Cuprtin</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
         <is>
           <t>SKU-A7E2719B8609</t>
         </is>
@@ -14537,7 +14922,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14699,6 +15084,11 @@
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
+        <is>
+          <t>Locain</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
         <is>
           <t>SKU-DDC4CEE3A29C</t>
         </is>
@@ -14719,7 +15109,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14889,6 +15279,11 @@
         </is>
       </c>
       <c r="AT79" t="inlineStr">
+        <is>
+          <t>Stamagen</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
         <is>
           <t>SKU-55E2DDF27BD8</t>
         </is>
@@ -14909,7 +15304,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15071,6 +15466,11 @@
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
+        <is>
+          <t>Pomalidomide BOS</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
         <is>
           <t>SKU-C350163F498C</t>
         </is>
@@ -15091,7 +15491,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15253,6 +15653,11 @@
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
+        <is>
+          <t>Pomalidomide BOS</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
         <is>
           <t>SKU-AC9A91DE065B</t>
         </is>
@@ -15273,7 +15678,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15439,6 +15844,11 @@
         </is>
       </c>
       <c r="AT82" t="inlineStr">
+        <is>
+          <t>Pomalidomide BOS</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
         <is>
           <t>SKU-763FA56036DB</t>
         </is>
@@ -15459,7 +15869,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15621,6 +16031,11 @@
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
+        <is>
+          <t>Pomalidomide BOS</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
         <is>
           <t>SKU-042DCCAE8802</t>
         </is>
@@ -15641,7 +16056,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15801,6 +16216,11 @@
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
+        <is>
+          <t>Teralas</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
         <is>
           <t>SKU-1F6E4E962048</t>
         </is>
@@ -15821,7 +16241,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15983,6 +16403,11 @@
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
+        <is>
+          <t>Sildenafil</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>SKU-CB4347A053EE</t>
         </is>
@@ -16003,7 +16428,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16167,6 +16592,11 @@
         </is>
       </c>
       <c r="AT86" t="inlineStr">
+        <is>
+          <t>Daglozin</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
         <is>
           <t>SKU-735D0FFFA518</t>
         </is>
@@ -16187,7 +16617,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16351,6 +16781,11 @@
         </is>
       </c>
       <c r="AT87" t="inlineStr">
+        <is>
+          <t>Daglozin</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
         <is>
           <t>SKU-47349A7CFF6F</t>
         </is>
@@ -16371,7 +16806,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16531,6 +16966,11 @@
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
+        <is>
+          <t>Epiduo Forte</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
         <is>
           <t>SKU-BB0253878964</t>
         </is>
@@ -16551,7 +16991,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16717,6 +17157,11 @@
         </is>
       </c>
       <c r="AT89" t="inlineStr">
+        <is>
+          <t>Essential D-3</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
         <is>
           <t>SKU-EF9AAEE083F7</t>
         </is>
@@ -16737,7 +17182,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16903,6 +17348,11 @@
         </is>
       </c>
       <c r="AT90" t="inlineStr">
+        <is>
+          <t>Essential D-3</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
         <is>
           <t>SKU-823E716EC41E</t>
         </is>
@@ -16923,7 +17373,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17087,6 +17537,11 @@
         </is>
       </c>
       <c r="AT91" t="inlineStr">
+        <is>
+          <t>Vizoden</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
         <is>
           <t>SKU-96D9F13447F0</t>
         </is>
@@ -17107,7 +17562,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17263,6 +17718,11 @@
       <c r="AR92" t="inlineStr"/>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
+        <is>
+          <t>Vizoden</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
         <is>
           <t>SKU-5612373BB869</t>
         </is>
@@ -17283,7 +17743,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17443,6 +17903,11 @@
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
+        <is>
+          <t>Vizoden</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
         <is>
           <t>SKU-7273CDABE678</t>
         </is>
@@ -17463,7 +17928,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17625,6 +18090,11 @@
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
+        <is>
+          <t>NERLYNX</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
         <is>
           <t>SKU-CEC0CD6ABF93</t>
         </is>
@@ -17645,7 +18115,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17805,6 +18275,11 @@
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
+        <is>
+          <t>Avogesic</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
         <is>
           <t>SKU-E808C8AD7F20</t>
         </is>
@@ -17825,7 +18300,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17987,6 +18462,11 @@
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
+        <is>
+          <t>Levogand</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
         <is>
           <t>SKU-AF4C42B58F38</t>
         </is>
@@ -18007,7 +18487,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18173,6 +18653,11 @@
         </is>
       </c>
       <c r="AT97" t="inlineStr">
+        <is>
+          <t>Levogand</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
         <is>
           <t>SKU-FA859F2AB405</t>
         </is>
@@ -18193,7 +18678,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18363,6 +18848,11 @@
         </is>
       </c>
       <c r="AT98" t="inlineStr">
+        <is>
+          <t>JARDIANCE 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
         <is>
           <t>SKU-B8B874E5CA67</t>
         </is>
@@ -18383,7 +18873,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18545,6 +19035,11 @@
       <c r="AR99" t="inlineStr"/>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
+        <is>
+          <t>JARDIANCE 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
         <is>
           <t>SKU-ADA88D407AB6</t>
         </is>
@@ -18565,7 +19060,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18725,6 +19220,11 @@
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
+        <is>
+          <t>Docrosa</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
         <is>
           <t>SKU-0D2DD38B3F11</t>
         </is>
@@ -18745,7 +19245,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18909,6 +19409,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Docrosa</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-67AD7EF0346E</t>
         </is>
@@ -18925,7 +19430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18971,100 +19476,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19096,7 +19606,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19111,92 +19621,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-13770</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>91.59</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>552</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19228,7 +19743,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19243,92 +19758,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-84613</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>174.63</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>553</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19360,7 +19880,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19375,92 +19895,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-75882</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>373.04</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>554</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19492,7 +20017,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19507,92 +20032,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-40463</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>142.94</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>555</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19624,7 +20154,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19639,92 +20169,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-31153</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>247.59</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>556</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19756,7 +20291,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19771,92 +20306,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-39867</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>429.98</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>557</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19888,7 +20428,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19903,92 +20443,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-49997</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>322.48</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>558</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20020,7 +20565,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20035,92 +20580,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-70678</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>120.69</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>559</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20152,7 +20702,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20167,92 +20717,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-58331</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>353.99</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>560</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20284,7 +20839,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20299,92 +20854,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-78173</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>183.13</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>561</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20416,7 +20976,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20431,92 +20991,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-43664</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>402.72</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>562</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20533,7 +21098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20639,6 +21204,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20674,7 +21249,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20739,6 +21314,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-48E328CA3C60</t>
         </is>
@@ -20775,7 +21360,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20840,6 +21425,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-38DC3D643B63</t>
         </is>
@@ -20876,7 +21471,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20941,6 +21536,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-C943ADDEBB1A</t>
         </is>
@@ -20977,7 +21582,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21042,6 +21647,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-160FAB38C593</t>
         </is>
@@ -21078,7 +21693,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21143,6 +21758,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-A3991467F43E</t>
         </is>
@@ -21179,7 +21804,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21244,6 +21869,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-0C0E1F15DF9A</t>
         </is>
@@ -21280,7 +21915,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21345,6 +21980,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-21DDACCD7AB8</t>
         </is>
@@ -21381,7 +22026,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21446,6 +22091,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-3AF2AB8B41F7</t>
         </is>
@@ -21482,7 +22137,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21547,6 +22202,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-74E9CF424569</t>
         </is>
@@ -21583,7 +22248,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21648,6 +22313,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-44C900230462</t>
         </is>
@@ -21684,7 +22359,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21749,6 +22424,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-A6ECE77EBE3E</t>
         </is>
@@ -21785,7 +22470,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21850,6 +22535,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-8ADDF5917244</t>
         </is>
@@ -21886,7 +22581,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21951,6 +22646,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-F35AFFA3DD4C</t>
         </is>
@@ -21987,7 +22692,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22052,6 +22757,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-4BEDCAB7D1F6</t>
         </is>
@@ -22088,7 +22803,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22153,6 +22868,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-DD781C2426B0</t>
         </is>
@@ -22189,7 +22914,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22254,6 +22979,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-56ABC065226C</t>
         </is>
@@ -22290,7 +23025,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22355,6 +23090,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-FE4C88597D36</t>
         </is>
@@ -22391,7 +23136,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22456,6 +23201,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-D64AC8E9DF1E</t>
         </is>
@@ -22492,7 +23247,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22557,6 +23312,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-932FD2B305E2</t>
         </is>
@@ -22593,7 +23358,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22658,6 +23423,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-7DF7DE9708A3</t>
         </is>

--- a/product_upload/packages/56/file.xlsx
+++ b/product_upload/packages/56/file.xlsx
@@ -682,8 +682,16 @@
           <t>0073836023-004-483595808355</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uroleph</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Uroleph detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -863,8 +871,16 @@
           <t>9288341032-624-347408394058</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uroleph</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Uroleph detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1048,8 +1064,16 @@
           <t>0029417544-744-190936313180</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Eptop</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Eptop detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Spectro Pharma) ALTAIF PHARMACEUTICALS COMPANY</t>
@@ -1227,8 +1251,16 @@
           <t>9620297643-547-278531454010</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Eptop</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Eptop detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Spectro Pharma) ALTAIF PHARMACEUTICALS COMPANY</t>
@@ -1406,8 +1438,16 @@
           <t>5957090792-244-186410472904</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Eptop</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Eptop detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Spectro Pharma) ALTAIF PHARMACEUTICALS COMPANY</t>
@@ -1589,8 +1629,16 @@
           <t>8915471052-134-381246860852</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uptravi 800 mcg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uptravi 800 mcg detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1726,7 +1774,7 @@
         </is>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>45798.39159722222</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -1772,8 +1820,16 @@
           <t>4226021415-917-783821788250</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Uptravi 400 mcg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Uptravi 400 mcg detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1909,7 +1965,7 @@
         </is>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>45798.3912037037</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -1963,8 +2019,16 @@
           <t>3377107202-974-732135255794</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lunginib</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Lunginib detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2096,7 +2160,7 @@
         </is>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>45410.67146990741</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -2152,12 +2216,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Adzoy 0.1 % &amp; 2.5 % Gel 30gm</t>
+          <t>وصف تفصيلي لـ Adzoy</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Adzoy 0.1 % &amp; 2.5 % Gel 30gm detailed description.</t>
+          <t>Adzoy detailed description.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -2341,12 +2405,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Tiotropium Eva 30 Cap Inhalation Powder</t>
+          <t>وصف تفصيلي لـ Tiotropium Eva</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tiotropium Eva 30 Cap Inhalation Powder detailed description.</t>
+          <t>Tiotropium Eva detailed description.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -2528,8 +2592,16 @@
           <t>3116003537-747-347785017121</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nyvepria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Nyvepria detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2669,7 +2741,7 @@
         </is>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>45729.48224537037</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -2719,8 +2791,16 @@
           <t>5192702353-139-469263791961</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Orfadin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Orfadin detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2856,7 +2936,7 @@
         </is>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>45653.89052083333</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -2910,8 +2990,16 @@
           <t>8492328329-928-526321877569</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sotyktu</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sotyktu detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3097,12 +3185,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Mucoplexil Syrup 150 ml</t>
+          <t>وصف تفصيلي لـ Mucoplexil</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mucoplexil Syrup 150 ml detailed description.</t>
+          <t>Mucoplexil detailed description.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -3240,7 +3328,7 @@
         </is>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>45433.4182175926</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -3294,8 +3382,16 @@
           <t>6480399242-026-057827175543</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Trientine dihydrochloride Tillomed</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Trientine dihydrochloride Tillomed detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3427,7 +3523,7 @@
         </is>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>45404.48082175926</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
@@ -3483,12 +3579,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Juleen 25 Mg 30 Tab</t>
+          <t>وصف تفصيلي لـ Juleen</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Juleen 25 Mg 30 Tab detailed description.</t>
+          <t>Juleen detailed description.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3678,12 +3774,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Juleen 50 Mg 30 Tab</t>
+          <t>وصف تفصيلي لـ Juleen</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Juleen 50 Mg 30 Tab detailed description.</t>
+          <t>Juleen detailed description.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -3867,12 +3963,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Juleen 100 Mg 30 Tab</t>
+          <t>وصف تفصيلي لـ Juleen</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Juleen 100 Mg 30 Tab detailed description.</t>
+          <t>Juleen detailed description.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4062,12 +4158,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Arify 10 Mg 30 Tablet</t>
+          <t>وصف تفصيلي لـ Arify</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Arify 10 Mg 30 Tablet detailed description.</t>
+          <t>Arify detailed description.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -4255,12 +4351,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Arify 15 Mg 30 Tablet</t>
+          <t>وصف تفصيلي لـ Arify</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Arify 15 Mg 30 Tablet detailed description.</t>
+          <t>Arify detailed description.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -4442,8 +4538,16 @@
           <t>1042470575-683-062520337190</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Jaypirca</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Jaypirca detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4579,7 +4683,7 @@
         </is>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>45532.57755787037</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP22" t="n">
         <v>0</v>
@@ -4629,8 +4733,16 @@
           <t>9918255508-977-959318413844</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ravopro</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ravopro detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4762,7 +4874,7 @@
         </is>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>45421.38219907408</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -4808,8 +4920,16 @@
           <t>4516302105-190-901337424605</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Warfarin Macleods</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Warfarin Macleods detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -4991,12 +5111,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Propylthiouracil Macleods 50 Mg 50 Tablet</t>
+          <t>وصف تفصيلي لـ Propylthiouracil MACLEODS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Propylthiouracil Macleods 50 Mg 50 Tablet detailed description.</t>
+          <t>Propylthiouracil MACLEODS detailed description.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -5180,12 +5300,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Tenival 10/160 Mg 28 Tab</t>
+          <t>وصف تفصيلي لـ Tenival</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tenival 10/160 Mg 28 Tab detailed description.</t>
+          <t>Tenival detailed description.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5371,12 +5491,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Tenival 5/160 Mg 28 Tab</t>
+          <t>وصف تفصيلي لـ Tenival</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tenival 5/160 Mg 28 Tab detailed description.</t>
+          <t>Tenival detailed description.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -5560,8 +5680,16 @@
           <t>7641569210-575-719030070657</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Trumavar</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Trumavar detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -5743,8 +5871,16 @@
           <t>6812873300-466-546782472534</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Trumavar</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Trumavar detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -5928,12 +6064,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Verkazia 1 Mg/Ml 120 Single-Dose Containers (0.3 Ml)</t>
+          <t>وصف تفصيلي لـ VERKAZIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Verkazia 1 Mg/Ml 120 Single-Dose Containers (0.3 Ml) detailed description.</t>
+          <t>VERKAZIA detailed description.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -6071,7 +6207,7 @@
         </is>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>45508.648125</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP30" t="n">
         <v>0</v>
@@ -6121,8 +6257,16 @@
           <t>3834481143-794-356400179215</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rivaroxaban MCP</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Rivaroxaban MCP detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6258,7 +6402,7 @@
         </is>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>45767.56396990741</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP31" t="n">
         <v>0</v>
@@ -6312,8 +6456,16 @@
           <t>1081373256-108-654571296122</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rivaroxaban MCP</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Rivaroxaban MCP detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6449,7 +6601,7 @@
         </is>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>45767.56357638889</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP32" t="n">
         <v>0</v>
@@ -6495,8 +6647,16 @@
           <t>1136451529-533-860477564570</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ataben</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Ataben detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6632,7 +6792,7 @@
         </is>
       </c>
       <c r="AO33" s="1" t="n">
-        <v>45439.56612268519</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP33" t="n">
         <v>0</v>
@@ -6682,8 +6842,16 @@
           <t>9379461680-427-974450464099</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ataben</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Ataben detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6819,7 +6987,7 @@
         </is>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>45439.56601851852</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP34" t="n">
         <v>0</v>
@@ -6869,8 +7037,16 @@
           <t>6667519568-634-595842583060</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Camzyos</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Camzyos detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7054,8 +7230,16 @@
           <t>9548641462-106-596948627258</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Camzyos</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Camzyos detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7243,8 +7427,16 @@
           <t>5877027041-594-360443260843</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Camzyos</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Camzyos detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7428,8 +7620,16 @@
           <t>3796748586-463-928272590750</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Camzyos</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Camzyos detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7615,12 +7815,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Calquence 100mg Film-Coated Tablet</t>
+          <t>وصف تفصيلي لـ Calquence</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Calquence 100mg Film-Coated Tablet detailed description.</t>
+          <t>Calquence detailed description.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -7762,7 +7962,7 @@
         </is>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>45470.43711805555</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP39" t="n">
         <v>0</v>
@@ -7812,8 +8012,16 @@
           <t>1803490924-932-152236656957</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bylvay</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bylvay detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7945,7 +8153,7 @@
         </is>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>45607.54905092593</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP40" t="n">
         <v>0</v>
@@ -7995,8 +8203,16 @@
           <t>6559248932-340-773479161508</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bylvay</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bylvay detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8128,7 +8344,7 @@
         </is>
       </c>
       <c r="AO41" s="1" t="n">
-        <v>45607.54739583333</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP41" t="n">
         <v>0</v>
@@ -8178,8 +8394,16 @@
           <t>2283178497-153-583992396064</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bylvay</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bylvay detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8311,7 +8535,7 @@
         </is>
       </c>
       <c r="AO42" s="1" t="n">
-        <v>45607.54833333333</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP42" t="n">
         <v>0</v>
@@ -8361,8 +8585,16 @@
           <t>4854132558-688-195964983275</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bylvay</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bylvay detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8494,7 +8726,7 @@
         </is>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>45607.54784722222</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP43" t="n">
         <v>0</v>
@@ -8546,12 +8778,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Bastix 10 Mg 50 Tablet</t>
+          <t>وصف تفصيلي لـ Bastix</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bastix 10 Mg 50 Tablet detailed description.</t>
+          <t>Bastix detailed description.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -8689,7 +8921,7 @@
         </is>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>45796.31079861111</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP44" t="n">
         <v>0</v>
@@ -8745,12 +8977,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Bastix 25 Mg 50 Tablet</t>
+          <t>وصف تفصيلي لـ Bastix</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bastix 25 Mg 50 Tablet detailed description.</t>
+          <t>Bastix detailed description.</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -8888,7 +9120,7 @@
         </is>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>45796.31048611111</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP45" t="n">
         <v>0</v>
@@ -8938,8 +9170,16 @@
           <t>8782743158-986-106338379758</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zelyssa 18 mg per 3 ml</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Zelyssa 18 mg per 3 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -9125,8 +9365,16 @@
           <t>1414031593-273-439312611671</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Evonanz 18 mg per 3 ml</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Evonanz 18 mg per 3 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -9308,8 +9556,16 @@
           <t>5217012623-150-466043389131</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Milorizast 10 mg  - 20 mg - 30 mg starter pack</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Milorizast 10 mg  - 20 mg - 30 mg starter pack detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">ALPHA PHARMA INDUSTRY </t>
@@ -9495,8 +9751,16 @@
           <t>0495338030-320-400691079807</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avysk HCT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Avysk HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9628,7 +9892,7 @@
         </is>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>45733.57289351852</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP49" t="n">
         <v>0</v>
@@ -9678,8 +9942,16 @@
           <t>8836233275-216-214443228816</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avysk HCT</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Avysk HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9811,7 +10083,7 @@
         </is>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>45733.57277777778</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP50" t="n">
         <v>0</v>
@@ -9865,8 +10137,16 @@
           <t>2886513034-686-127199516734</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avysk HCT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Avysk HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -9998,7 +10278,7 @@
         </is>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>45704.53015046296</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP51" t="n">
         <v>0</v>
@@ -10052,8 +10332,16 @@
           <t>0443967701-849-545702178433</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SUNLENCA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SUNLENCA detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10245,8 +10533,16 @@
           <t>5059349672-979-088524165575</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SUNLENCA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SUNLENCA detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10386,7 +10682,7 @@
         </is>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>45448.6622337963</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP53" t="n">
         <v>0</v>
@@ -10436,8 +10732,16 @@
           <t>7753066317-983-078261465912</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Racitam</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Racitam detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10617,8 +10921,16 @@
           <t>8432789261-589-853316947048</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cymbatex</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Cymbatex detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10750,7 +11062,7 @@
         </is>
       </c>
       <c r="AO55" s="1" t="n">
-        <v>45777.55915509259</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP55" t="n">
         <v>0</v>
@@ -10800,8 +11112,16 @@
           <t>6780720130-889-461430933916</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cymbatex</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Cymbatex detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10933,7 +11253,7 @@
         </is>
       </c>
       <c r="AO56" s="1" t="n">
-        <v>45777.55888888889</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP56" t="n">
         <v>0</v>
@@ -10985,12 +11305,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Olmy 20 Mg 30 Tab</t>
+          <t>وصف تفصيلي لـ Olmy</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Olmy 20 Mg 30 Tab detailed description.</t>
+          <t>Olmy detailed description.</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -11178,12 +11498,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Olmy 40 Mg 30 Tab</t>
+          <t>وصف تفصيلي لـ Olmy</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Olmy 40 Mg 30 Tab detailed description.</t>
+          <t>Olmy detailed description.</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -11365,8 +11685,16 @@
           <t>1652196490-541-020661772943</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PORENZA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PORENZA detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -11500,7 +11828,7 @@
         </is>
       </c>
       <c r="AO59" s="1" t="n">
-        <v>45449.55510416667</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP59" t="n">
         <v>0</v>
@@ -11556,12 +11884,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ PORENZA 400mg</t>
+          <t>وصف تفصيلي لـ PORENZA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>PORENZA 400mg detailed description.</t>
+          <t>PORENZA detailed description.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -11697,7 +12025,7 @@
         </is>
       </c>
       <c r="AO60" s="1" t="n">
-        <v>45449.55502314815</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP60" t="n">
         <v>2250</v>
@@ -11747,8 +12075,16 @@
           <t>4144741620-296-516236181203</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hydroxychloroquine SAJA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Hydroxychloroquine SAJA detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11880,7 +12216,7 @@
         </is>
       </c>
       <c r="AO61" s="1" t="n">
-        <v>45595.38115740741</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP61" t="n">
         <v>0</v>
@@ -11934,8 +12270,16 @@
           <t>5993389705-384-830709476013</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sesmo</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sesmo detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12115,8 +12459,16 @@
           <t>1523980138-906-242892549650</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sesmo</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sesmo detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12296,8 +12648,16 @@
           <t>5972071629-389-523288879105</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sesmo</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sesmo detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12429,7 +12789,7 @@
         </is>
       </c>
       <c r="AO64" s="1" t="n">
-        <v>45483.59980324074</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP64" t="n">
         <v>0</v>
@@ -12483,8 +12843,16 @@
           <t>5998005022-664-525524747405</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sesmo</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sesmo detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12664,8 +13032,16 @@
           <t>7052744083-611-998080073539</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Simvagen Plus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Simvagen Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12849,8 +13225,16 @@
           <t>2326529816-815-791257723150</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Simvagen Plus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Simvagen Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13038,8 +13422,16 @@
           <t>9240186736-542-209590218196</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nervamine</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Nervamine detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13179,7 +13571,7 @@
         </is>
       </c>
       <c r="AO68" s="1" t="n">
-        <v>45811.64905092592</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP68" t="n">
         <v>0</v>
@@ -13227,12 +13619,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Jusprin 81 Mg Tablet 90 Pcs</t>
+          <t>وصف تفصيلي لـ Jusprin</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Jusprin 81 Mg Tablet 90 Pcs detailed description.</t>
+          <t>Jusprin detailed description.</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -13370,7 +13762,7 @@
         </is>
       </c>
       <c r="AO69" s="1" t="n">
-        <v>45552.53238425926</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP69" t="n">
         <v>0</v>
@@ -13420,8 +13812,16 @@
           <t>7945278499-366-600984397240</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Floxmed</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Floxmed detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13561,7 +13961,7 @@
         </is>
       </c>
       <c r="AO70" s="1" t="n">
-        <v>45811.64931712963</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP70" t="n">
         <v>0</v>
@@ -13615,8 +14015,16 @@
           <t>5473937511-528-442423145343</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vizarsin</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Vizarsin detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13752,7 +14160,7 @@
         </is>
       </c>
       <c r="AO71" s="1" t="n">
-        <v>45669.42084490741</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP71" t="n">
         <v>0</v>
@@ -13804,12 +14212,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Sogroya 15mg/1.5ml Pre-Filled Pen (Refrigrator )</t>
+          <t>وصف تفصيلي لـ Sogroya 15 mg / 1.5 ml</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Sogroya 15mg/1.5ml Pre-Filled Pen (Refrigrator ) detailed description.</t>
+          <t>Sogroya 15 mg / 1.5 ml detailed description.</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -13943,7 +14351,7 @@
         </is>
       </c>
       <c r="AO72" s="1" t="n">
-        <v>45496.45746527778</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP72" t="n">
         <v>0</v>
@@ -13997,8 +14405,16 @@
           <t>5857215386-578-956429942226</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Famotidine for oral suspension</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Famotidine for oral suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14182,8 +14598,16 @@
           <t>3120072173-274-715856916440</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Famotidine Amarox</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Famotidine Amarox detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14371,8 +14795,16 @@
           <t>0482803573-475-381690085418</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Akeega</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Akeega detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14560,8 +14992,16 @@
           <t>9861370791-017-734663408232</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Akeega</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Akeega detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14741,8 +15181,16 @@
           <t>0467816157-656-944615591224</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cuprtin</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Cuprtin detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14930,8 +15378,16 @@
           <t>3449768222-420-108097623253</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Locain</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Locain detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15067,7 +15523,7 @@
         </is>
       </c>
       <c r="AO78" s="1" t="n">
-        <v>45470.53274305556</v>
+        <v>25569.12552083334</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -15117,8 +15573,16 @@
           <t>2378203663-037-226211089552</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Stamagen</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Stamagen detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15258,7 +15722,7 @@
         </is>
       </c>
       <c r="AO79" s="1" t="n">
-        <v>45505.55861111111</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -15312,8 +15776,16 @@
           <t>2945232161-678-902530268882</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pomalidomide BOS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Pomalidomide BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15449,7 +15921,7 @@
         </is>
       </c>
       <c r="AO80" s="1" t="n">
-        <v>45832.58519675926</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -15499,8 +15971,16 @@
           <t>3308930981-108-562032367162</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pomalidomide BOS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Pomalidomide BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15636,7 +16116,7 @@
         </is>
       </c>
       <c r="AO81" s="1" t="n">
-        <v>45832.58519675926</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP81" t="n">
         <v>0</v>
@@ -15686,8 +16166,16 @@
           <t>7040314424-202-512492210397</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pomalidomide BOS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Pomalidomide BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -15823,7 +16311,7 @@
         </is>
       </c>
       <c r="AO82" s="1" t="n">
-        <v>45832.58288194444</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -15877,8 +16365,16 @@
           <t>6974560145-534-962587403096</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pomalidomide BOS</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Pomalidomide BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16014,7 +16510,7 @@
         </is>
       </c>
       <c r="AO83" s="1" t="n">
-        <v>45832.58288194444</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -16064,8 +16560,16 @@
           <t>9355047712-871-837488625474</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Teralas</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Teralas detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16249,8 +16753,16 @@
           <t>4887864001-860-374892518019</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sildenafil</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sildenafil detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16386,7 +16898,7 @@
         </is>
       </c>
       <c r="AO85" s="1" t="n">
-        <v>45501.38707175926</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP85" t="n">
         <v>0</v>
@@ -16436,8 +16948,16 @@
           <t>4217550358-499-273716246236</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Daglozin</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Daglozin detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16625,8 +17145,16 @@
           <t>7325293515-329-019360389513</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Daglozin</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Daglozin detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16814,8 +17342,16 @@
           <t>0716798294-654-386929786604</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Epiduo Forte</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Epiduo Forte detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17001,12 +17537,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Essential D3 5000 Iu 100 Capsules</t>
+          <t>وصف تفصيلي لـ Essential D-3</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Essential D3 5000 Iu 100 Capsules detailed description.</t>
+          <t>Essential D-3 detailed description.</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -17136,7 +17672,7 @@
         </is>
       </c>
       <c r="AO89" s="1" t="n">
-        <v>45776.3987037037</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP89" t="n">
         <v>21</v>
@@ -17192,12 +17728,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Essential D3 10000 Iu 100 Capsules</t>
+          <t>وصف تفصيلي لـ Essential D-3</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Essential D3 10000 Iu 100 Capsules detailed description.</t>
+          <t>Essential D-3 detailed description.</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -17327,7 +17863,7 @@
         </is>
       </c>
       <c r="AO90" s="1" t="n">
-        <v>45776.3984375</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP90" t="n">
         <v>24</v>
@@ -17381,8 +17917,16 @@
           <t>4172127443-254-412950234126</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vizoden</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Vizoden detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17570,8 +18114,16 @@
           <t>8096444007-413-191107992366</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vizoden</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Vizoden detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17751,8 +18303,16 @@
           <t>9015272590-277-548488838009</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vizoden</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Vizoden detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17936,8 +18496,16 @@
           <t>4878305232-043-042592640489</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NERLYNX</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>NERLYNX detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18073,7 +18641,7 @@
         </is>
       </c>
       <c r="AO94" s="1" t="n">
-        <v>45691.5035300926</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP94" t="n">
         <v>0</v>
@@ -18123,8 +18691,16 @@
           <t>1298699261-898-754128620193</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avogesic</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Avogesic detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18308,8 +18884,16 @@
           <t>7168942765-621-428775819133</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Levogand</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Levogand detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18445,7 +19029,7 @@
         </is>
       </c>
       <c r="AO96" s="1" t="n">
-        <v>45785.745</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP96" t="n">
         <v>0</v>
@@ -18495,8 +19079,16 @@
           <t>7720120640-458-332376813878</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Levogand</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Levogand detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18632,7 +19224,7 @@
         </is>
       </c>
       <c r="AO97" s="1" t="n">
-        <v>45785.74489583333</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP97" t="n">
         <v>0</v>
@@ -18688,12 +19280,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Jardiance Tablets 10 mg 30 Tab</t>
+          <t>وصف تفصيلي لـ JARDIANCE 10 mg film-coated tablet</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Jardiance Tablets 10 mg 30 Tab detailed description.</t>
+          <t>JARDIANCE 10 mg film-coated tablet detailed description.</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -18827,7 +19419,7 @@
         </is>
       </c>
       <c r="AO98" s="1" t="n">
-        <v>45608.64333333333</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP98" t="n">
         <v>46.5</v>
@@ -18883,12 +19475,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>وصف تفصيلي لـ Jardiance Tablets 25 mg 30 Tab</t>
+          <t>وصف تفصيلي لـ JARDIANCE 25 mg film-coated tablet</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Jardiance Tablets 25 mg 30 Tab detailed description.</t>
+          <t>JARDIANCE 25 mg film-coated tablet detailed description.</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -19022,7 +19614,7 @@
         </is>
       </c>
       <c r="AO99" s="1" t="n">
-        <v>45608.64386574074</v>
+        <v>25569.12553240741</v>
       </c>
       <c r="AP99" t="n">
         <v>46.5</v>
@@ -19068,8 +19660,16 @@
           <t>1208104372-775-687688192171</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Docrosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Docrosa detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19253,8 +19853,16 @@
           <t>6849012813-869-006942123792</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Docrosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Docrosa detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
@@ -21098,7 +21706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21174,45 +21782,50 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>Size *</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Manufacturer Name</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21287,43 +21900,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>100</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>109.68</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-48E328CA3C60</t>
         </is>
@@ -21398,43 +22016,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>100</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>312.99</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-38DC3D643B63</t>
         </is>
@@ -21509,43 +22132,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>100</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>244.44</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-C943ADDEBB1A</t>
         </is>
@@ -21620,43 +22248,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>100</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>159.51</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-160FAB38C593</t>
         </is>
@@ -21731,43 +22364,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>100</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>435.48</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-A3991467F43E</t>
         </is>
@@ -21842,43 +22480,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>100</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>204.33</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-0C0E1F15DF9A</t>
         </is>
@@ -21953,43 +22596,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>100</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>47.39</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-21DDACCD7AB8</t>
         </is>
@@ -22064,43 +22712,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>100</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>423.94</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-3AF2AB8B41F7</t>
         </is>
@@ -22175,43 +22828,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>100</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>272.79</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-74E9CF424569</t>
         </is>
@@ -22286,43 +22944,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>100</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>221.44</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-44C900230462</t>
         </is>
@@ -22397,43 +23060,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>100</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>311.1</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-A6ECE77EBE3E</t>
         </is>
@@ -22508,43 +23176,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>100</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>84.48</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-8ADDF5917244</t>
         </is>
@@ -22619,43 +23292,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>100</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>370.53</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-F35AFFA3DD4C</t>
         </is>
@@ -22730,43 +23408,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
         <v>100</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>34.53</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-4BEDCAB7D1F6</t>
         </is>
@@ -22841,43 +23524,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
         <v>100</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>89.54000000000001</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-DD781C2426B0</t>
         </is>
@@ -22952,43 +23640,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
         <v>100</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>52.67</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-56ABC065226C</t>
         </is>
@@ -23063,43 +23756,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
         <v>100</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>72.43000000000001</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-FE4C88597D36</t>
         </is>
@@ -23174,43 +23872,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
         <v>100</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>128.39</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-D64AC8E9DF1E</t>
         </is>
@@ -23285,43 +23988,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
         <v>100</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>125.02</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-932FD2B305E2</t>
         </is>
@@ -23396,43 +24104,48 @@
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
         <v>100</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>177.47</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-7DF7DE9708A3</t>
         </is>

--- a/product_upload/packages/56/file.xlsx
+++ b/product_upload/packages/56/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20084,7 +20084,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21817,7 +21817,7 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
